--- a/files/九龙-茶果岭、油塘及鲤鱼门-KOKO HILLS.xlsx
+++ b/files/九龙-茶果岭、油塘及鲤鱼门-KOKO HILLS.xlsx
@@ -8,9 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座 销控表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -113,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -178,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,54 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -713,7 +569,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-28</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -759,7 +615,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-03</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -1081,7 +937,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-15</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1219,7 +1075,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-09</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1265,7 +1121,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1357,7 +1213,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-02</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1449,7 +1305,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-07</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1495,7 +1351,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-05</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1633,7 +1489,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1725,7 +1581,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1821,7 +1677,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-30</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1913,7 +1769,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-20</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2005,7 +1861,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-07</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2101,7 +1957,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-22</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2193,7 +2049,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-05</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2469,7 +2325,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-07</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2561,7 +2417,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-22</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2653,7 +2509,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2745,7 +2601,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-04</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2837,7 +2693,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-11</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2883,7 +2739,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3021,7 +2877,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3163,7 +3019,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3209,7 +3065,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3301,7 +3157,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3393,7 +3249,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3439,7 +3295,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3669,7 +3525,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-03</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3949,7 +3805,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -3995,7 +3851,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4225,7 +4081,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4271,7 +4127,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5123,7 +4979,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5169,7 +5025,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-25</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5933,7 +5789,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -6121,7 +5977,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6305,7 +6161,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6539,7 +6395,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6635,7 +6491,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6681,7 +6537,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6727,7 +6583,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -6773,7 +6629,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -6819,7 +6675,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -6865,7 +6721,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -6911,7 +6767,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-03</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -6957,7 +6813,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -7003,7 +6859,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-12-08</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -7049,7 +6905,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-25</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -7095,7 +6951,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7187,7 +7043,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7279,7 +7135,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-07</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -7325,7 +7181,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -7371,7 +7227,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7417,7 +7273,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -7463,7 +7319,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-09</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -7509,7 +7365,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -7555,7 +7411,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -7647,7 +7503,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -7693,7 +7549,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -7789,7 +7645,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -7835,7 +7691,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -7881,7 +7737,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -8019,7 +7875,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -8065,7 +7921,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -8111,7 +7967,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-26</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -8157,7 +8013,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-04</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -8203,7 +8059,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -8249,7 +8105,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -8341,7 +8197,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -8437,7 +8293,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -8483,7 +8339,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -8529,7 +8385,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -8575,7 +8431,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -8621,7 +8477,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -8667,7 +8523,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-26</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -8713,7 +8569,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -8809,7 +8665,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-03</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -8855,7 +8711,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -8901,7 +8757,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -8947,7 +8803,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -8993,7 +8849,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-13</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -9089,7 +8945,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -9135,7 +8991,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-03</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -9181,7 +9037,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -9227,7 +9083,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-10</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -9319,7 +9175,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -9365,7 +9221,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-05</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -9595,7 +9451,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -9641,7 +9497,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -9687,7 +9543,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -9825,7 +9681,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -9871,7 +9727,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-14</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -9917,7 +9773,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -9963,7 +9819,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -10009,7 +9865,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-09</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -10055,7 +9911,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -10101,7 +9957,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -10147,7 +10003,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -10239,7 +10095,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -10285,7 +10141,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -10331,7 +10187,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -10377,7 +10233,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -10423,7 +10279,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-03-31</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -10565,7 +10421,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -10611,7 +10467,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -10657,7 +10513,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -10703,7 +10559,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-03</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -10749,7 +10605,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-09</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -10795,7 +10651,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -10891,7 +10747,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -10937,7 +10793,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -10983,7 +10839,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -11125,7 +10981,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-10</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -11171,7 +11027,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -11317,7 +11173,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-03</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -11363,7 +11219,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -11409,7 +11265,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-25</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -11505,7 +11361,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-23</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -11551,7 +11407,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -11693,7 +11549,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-02-23</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -11739,7 +11595,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -11785,7 +11641,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-04-25</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -11881,7 +11737,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -11927,7 +11783,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-02-03</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -12069,7 +11925,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-21</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -12115,7 +11971,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-04</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -12161,7 +12017,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-09-29</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -12257,7 +12113,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-06</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -12303,7 +12159,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -12349,7 +12205,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-07</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -12441,7 +12297,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -12487,7 +12343,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -12533,7 +12389,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -12629,7 +12485,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -12675,7 +12531,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -12817,7 +12673,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -12863,7 +12719,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -13005,7 +12861,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-03</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -13051,7 +12907,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -13193,7 +13049,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -13239,7 +13095,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -13381,7 +13237,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -13523,7 +13379,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -13569,7 +13425,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -13615,7 +13471,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -13707,7 +13563,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-28</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -13753,7 +13609,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -13845,7 +13701,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -13937,7 +13793,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -13983,7 +13839,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-24</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -14121,7 +13977,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -14167,7 +14023,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-03</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -14355,7 +14211,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -14493,7 +14349,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-21</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -14539,7 +14395,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-11-08</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -14585,7 +14441,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -14631,7 +14487,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -14773,7 +14629,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-30</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -14865,7 +14721,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -14911,7 +14767,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -14957,7 +14813,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-04-03</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -15095,7 +14951,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-25</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -15187,7 +15043,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-17</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -15379,7 +15235,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -15471,7 +15327,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-04</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -15517,7 +15373,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -15659,7 +15515,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -15705,7 +15561,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -15751,7 +15607,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-08</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -15797,7 +15653,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -15939,7 +15795,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-04-21</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -16035,7 +15891,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-26</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -16081,7 +15937,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -16127,7 +15983,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-26</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -16219,7 +16075,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-11-08</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -16311,7 +16167,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -16357,7 +16213,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -16403,7 +16259,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-09</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -16495,7 +16351,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-29</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -16587,7 +16443,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -16633,7 +16489,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-02</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -16679,7 +16535,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -16817,7 +16673,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-17</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -16863,7 +16719,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -16909,7 +16765,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -16955,7 +16811,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -17139,7 +16995,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -17185,7 +17041,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -17231,7 +17087,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -17277,7 +17133,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -17415,7 +17271,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-13</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -17461,7 +17317,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -17507,7 +17363,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-25</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -17553,7 +17409,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-20</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -17599,7 +17455,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -17737,7 +17593,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-22</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -17783,7 +17639,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-04</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -17829,7 +17685,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -18013,7 +17869,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-19</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -18109,7 +17965,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -18155,7 +18011,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -18293,7 +18149,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -18339,7 +18195,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-04-28</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -18385,7 +18241,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-26</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -18573,7 +18429,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -18619,7 +18475,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -18665,7 +18521,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -18849,7 +18705,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -18895,7 +18751,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -18941,7 +18797,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -19125,7 +18981,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -19171,7 +19027,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -19309,7 +19165,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-17</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -19401,7 +19257,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -19447,7 +19303,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -19539,7 +19395,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="H408" s="5" t="n">
@@ -19631,7 +19487,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-27</t>
         </is>
       </c>
       <c r="H410" s="5" t="n">
@@ -19677,7 +19533,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-20</t>
         </is>
       </c>
       <c r="H411" s="5" t="n">
@@ -19723,7 +19579,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-07</t>
         </is>
       </c>
       <c r="H412" s="5" t="n">
@@ -19861,7 +19717,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="H415" s="5" t="n">
@@ -19883,4228 +19739,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KOKO HILLS - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>123 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>16 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>105 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 725呎 (3房)
-$1,805万
-$24,894/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>E | 736呎 (3房)
-$1,754万
-$23,832/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>F | 522呎 (2房)
-$1,269万
-$24,310/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t>G | 570呎 (3房)
-$1,471万
-$25,800/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>23&amp;25/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 2024呎 (4+房)
-$6,274万
-$31,000/呎
-(20年-07月)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 1780呎 (4+房)
-$4,800万
-$26,966/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr"/>
-      <c r="G7" s="16" t="inlineStr"/>
-      <c r="H7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr"/>
-      <c r="C8" s="16" t="inlineStr"/>
-      <c r="D8" s="16" t="inlineStr"/>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>D | 671呎 (3房)
-$1,332万
-$19,851/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>E | 736呎 (3房)
-$1,470万
-$19,973/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>F | 522呎 (2房)
-$1,074万
-$20,579/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>G | 570呎 (3房)
-$1,177万
-$20,642/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 1300呎 (4+房)
-$2,659万
-$20,457/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,140万
-$23,802/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 671呎 (3房)
-$1,339万
-$19,954/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,732万
-$23,494/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>F | 522呎 (2房)
-$1,152万
-$22,073/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>G | 570呎 (3房)
-$1,156万
-$20,272/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 1300呎 (4+房)
-$3,033万
-$23,331/呎
-(23年-12月)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,116万
-$23,533/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr"/>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>D | 671呎 (3房)
-$1,330万
-$19,821/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>E | 736呎 (3房)
-$1,460万
-$19,840/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>F | 522呎 (2房)
-$1,156万
-$22,151/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>G | 570呎 (3房)
-$1,247万
-$21,884/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 1300呎 (4+房)
-$2,538万
-$19,523/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,097万
-$23,324/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr"/>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 671呎 (3房)
-$1,358万
-$20,231/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,639万
-$22,233/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 522呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>G | 584呎 (3房)
-$1,248万
-$21,368/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 1300呎 (4+房)
-$2,783万
-$21,408/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,114万
-$23,513/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr"/>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 671呎 (3房)
-$1,354万
-$20,171/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,674万
-$22,708/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 522呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>G | 584呎 (3房)
-$1,253万
-$21,450/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 1300呎 (4+房)
-$2,550万
-$19,615/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,146万
-$23,873/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr"/>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 671呎 (3房)
-$1,310万
-$19,523/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>E | 736呎 (2房)
-$1,681万
-$22,840/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 522呎 (2房)
-$1,058万
-$20,261/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>G | 584呎 (3房)
-$1,130万
-$19,342/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 1300呎 (4+房)
-$2,554万
-$19,646/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,116万
-$23,539/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr"/>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 671呎 (3房)
-$1,341万
-$19,991/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,613万
-$21,882/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>F | 522呎 (2房)
-$1,031万
-$19,745/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>G | 584呎 (3房)
-$1,253万
-$21,461/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 1300呎 (4+房)
-$2,550万
-$19,615/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,082万
-$23,155/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr"/>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 671呎 (3房)
-$1,300万
-$19,374/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>E | 736呎 (3房)
-$1,647万
-$22,379/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>F | 522呎 (2房)
-$1,074万
-$20,573/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>G | 584呎 (3房)
-$1,282万
-$21,952/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 1300呎 (4+房)
-$2,565万
-$19,731/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,048万
-$22,781/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr"/>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 671呎 (3房)
-$1,333万
-$19,870/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,592万
-$21,598/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>F | 522呎 (2房)
-$1,097万
-$21,013/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>G | 584呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 1300呎 (4+房)
-$2,558万
-$19,678/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,089万
-$23,236/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr"/>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 671呎 (3房)
-$1,330万
-$19,821/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>E | 736呎 (3房)
-$1,431万
-$19,440/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>F | 522呎 (2房)
-$1,065万
-$20,410/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>G | 584呎 (3房)
-$1,196万
-$20,474/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 1300呎 (4+房)
-$2,576万
-$19,814/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$1,765万
-$19,633/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr"/>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 671呎 (3房)
-$1,325万
-$19,753/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>E | 736呎 (3房)
-$1,391万
-$18,899/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 522呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>G | 584呎 (3房)
-$1,267万
-$21,690/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 1300呎 (4+房)
-$2,568万
-$19,755/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$1,708万
-$18,999/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr"/>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 671呎 (3房)
-$1,321万
-$19,693/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>E | 736呎 (3房)
-$1,410万
-$19,158/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>F | 522呎 (2房)
-$1,057万
-$20,247/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>G | 584呎 (3房)
-$1,213万
-$20,777/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 1300呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$1,702万
-$18,932/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr"/>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 671呎 (3房)
-$1,318万
-$19,635/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 736呎 (3房)
-$1,420万
-$19,287/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 522呎 (2房)
-$1,053万
-$20,167/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>G | 584呎 (3房)
-$1,224万
-$20,954/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 1300呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$1,720万
-$19,132/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr"/>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 671呎 (3房)
-$1,300万
-$19,382/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>E | 736呎 (3房)
-$1,415万
-$19,230/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 522呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>G | 584呎 (3房)
-$1,093万
-$18,712/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 1300呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$1,707万
-$18,988/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr"/>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 671呎 (3房)
-$1,293万
-$19,265/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,595万
-$21,647/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>F | 522呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>G | 584呎 (3房)
-$1,104万
-$18,901/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 1300呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$1,719万
-$19,120/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr"/>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 671呎 (3房)
-$1,289万
-$19,209/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,542万
-$20,920/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>F | 522呎 (2房)
-$1,062万
-$20,354/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H23" s="18" t="inlineStr">
-        <is>
-          <t>G | 584呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 1300呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$1,714万
-$19,063/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr"/>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 671呎 (3房)
-$1,324万
-$19,729/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,416万
-$19,220/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F | 522呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H24" s="18" t="inlineStr">
-        <is>
-          <t>G | 584呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>A | 1300呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr"/>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 671呎 (3房)
-$1,294万
-$19,285/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>E | 736呎 (3房)
-$1,390万
-$18,886/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 522呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>G | 570呎 (3房)
-$1,078万
-$18,921/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr"/>
-      <c r="C26" s="16" t="inlineStr"/>
-      <c r="D26" s="16" t="inlineStr"/>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 652呎 (3房)
-$1,307万
-$20,046/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>E | 736呎 (3房)
-$1,451万
-$19,709/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 522呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>G | 546呎 (3房)
-$1,074万
-$19,674/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr"/>
-      <c r="C27" s="16" t="inlineStr"/>
-      <c r="D27" s="16" t="inlineStr"/>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 634呎 (3房)
-$1,528万
-$24,106/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,519万
-$21,856/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>F | 501呎 (2房)
-$1,052万
-$20,994/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>G | 524呎 (3房)
-$1,134万
-$21,641/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>1&amp;2/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 1850呎 (4+房)
-$4,250万
-$22,975/呎
-(20年-07月)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 1518呎 (4+房)
-$2,940万
-$19,368/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 1212呎 (4+房)
-$2,968万
-$24,488/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr"/>
-      <c r="F28" s="16" t="inlineStr"/>
-      <c r="G28" s="16" t="inlineStr"/>
-      <c r="H28" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:I26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KOKO HILLS - 3座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>164 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>22 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>140 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>A | 1223呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 1102呎 (3房)
-$2,880万
-$26,134/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr"/>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>E | 1073呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr"/>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t>G | 1068呎 (3房)
-$2,583万
-$24,185/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,796万
-$23,329/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 466呎 (2房)
-$1,069万
-$22,938/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>C | 366呎 (1房)
-$867万
-$23,680/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>D | 769呎 (3房)
-$1,671万
-$21,727/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>E | 521呎 (2房)
-$1,205万
-$23,129/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>F | 444呎 (2房)
-$964万
-$21,723/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>G | 459呎 (2房)
-$1,000万
-$21,791/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$1,134万
-$21,813/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-$1,741万
-$22,576/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 466呎 (2房)
-$1,049万
-$22,511/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 366呎 (1房)
-$1,067万
-$29,161/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>D | 769呎 (3房)
-$1,664万
-$21,640/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>E | 521呎 (2房)
-$1,128万
-$21,658/呎
-(20年-07月)</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>F | 444呎 (2房)
-$997万
-$22,464/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>G | 459呎 (2房)
-$996万
-$21,704/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$1,158万
-$22,279/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,786万
-$23,200/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 466呎 (2房)
-$1,099万
-$23,575/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 366呎 (1房)
-$878万
-$23,997/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 769呎 (3房)
-$1,657万
-$21,553/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>E | 521呎 (2房)
-$1,118万
-$21,466/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>F | 444呎 (2房)
-$982万
-$22,126/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>G | 459呎 (2房)
-$1,019万
-$22,196/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$1,120万
-$21,533/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,668万
-$21,664/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 465呎 (2房)
-$1,026万
-$22,060/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 366呎 (1房)
-$1,062万
-$29,014/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>D | 770呎 (3房)
-$1,500万
-$19,481/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>E | 521呎 (2房)
-$1,103万
-$21,169/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>F | 462呎 (2房)
-$964万
-$20,877/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>G | 463呎 (2房)
-$1,000万
-$21,598/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I10" s="18" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,662万
-$21,578/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 466呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 366呎 (1房)
-$832万
-$22,721/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 770呎 (3房)
-$1,496万
-$19,429/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>E | 521呎 (2房)
-$1,082万
-$20,774/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>F | 462呎 (2房)
-$959万
-$20,753/呎
-(23年-10月)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>G | 463呎 (2房)
-$995万
-$21,482/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$1,084万
-$20,840/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,760万
-$22,860/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 466呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 366呎 (1房)
-$830万
-$22,667/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 769呎 (3房)
-$1,675万
-$21,784/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>E | 521呎 (2房)
-$1,078万
-$20,691/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 462呎 (2房)
-$955万
-$20,669/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>G | 463呎 (2房)
-$1,021万
-$22,056/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$1,134万
-$21,813/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,642万
-$21,321/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 466呎 (2房)
-$1,010万
-$21,665/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 366呎 (1房)
-$824万
-$22,516/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 769呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>E | 521呎 (2房)
-$1,097万
-$21,050/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 462呎 (2房)
-$947万
-$20,506/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>G | 463呎 (2房)
-$952万
-$20,570/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$1,071万
-$20,592/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-$1,656万
-$21,479/呎
-(20年-07月)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 466呎 (2房)
-$1,006万
-$21,579/呎
-(20年-07月)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 366呎 (1房)
-$864万
-$23,607/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 770呎 (3房)
-$1,506万
-$19,565/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>E | 521呎 (2房)
-$1,065万
-$20,445/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>F | 462呎 (2房)
-$944万
-$20,424/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>G | 463呎 (2房)
-$949万
-$20,488/呎
-(20年-07月)</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$1,066万
-$20,510/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,681万
-$21,826/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 466呎 (2房)
-$1,017万
-$21,815/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 366呎 (1房)
-$872万
-$23,833/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 770呎 (3房)
-$1,502万
-$19,506/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>E | 521呎 (2房)
-$1,029万
-$19,754/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>F | 462呎 (2房)
-$1,000万
-$21,639/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>G | 463呎 (2房)
-$945万
-$20,406/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$1,062万
-$20,427/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,622万
-$21,068/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 466呎 (2房)
-$998万
-$21,406/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 366呎 (1房)
-$860万
-$23,489/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 769呎 (3房)
-$1,708万
-$22,205/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>E | 521呎 (2房)
-$1,057万
-$20,282/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>F | 462呎 (2房)
-$996万
-$21,552/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t>G | 463呎 (2房)
-$965万
-$20,842/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I16" s="17" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$1,092万
-$20,994/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,616万
-$20,983/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 466呎 (2房)
-$994万
-$21,322/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 366呎 (1房)
-$816万
-$22,295/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 770呎 (3房)
-$1,529万
-$19,853/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 521呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>F | 462呎 (2房)
-$932万
-$20,182/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>G | 463呎 (2房)
-$997万
-$21,533/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$1,054万
-$20,265/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,650万
-$21,432/呎
-(20年-07月)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 465呎 (2房)
-$990万
-$21,282/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 366呎 (1房)
-$864万
-$23,620/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 769呎 (3房)
-$1,593万
-$20,710/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 521呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>F | 462呎 (2房)
-$988万
-$21,381/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>G | 463呎 (2房)
-$963万
-$20,806/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-$1,050万
-$20,185/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,654万
-$21,479/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 465呎 (2房)
-$986万
-$21,198/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 366呎 (1房)
-$810万
-$22,117/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 769呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 521呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>F | 462呎 (2房)
-$984万
-$21,294/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>G | 463呎 (2房)
-$960万
-$20,724/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I19" s="18" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,596万
-$20,734/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 466呎 (2房)
-$982万
-$21,069/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 366呎 (1房)
-$837万
-$22,872/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 769呎 (3房)
-$1,580万
-$20,545/呎
-(20年-07月)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 521呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 462呎 (2房)
-$980万
-$21,210/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>G | 463呎 (2房)
-$956万
-$20,641/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-$1,584万
-$20,542/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 465呎 (2房)
-$974万
-$20,946/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 366呎 (1房)
-$825万
-$22,552/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 770呎 (3房)
-$1,486万
-$19,292/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 521呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 462呎 (2房)
-$949万
-$20,539/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>G | 463呎 (2房)
-$977万
-$21,108/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I21" s="18" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-$1,578万
-$20,460/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 466呎 (2房)
-$970万
-$20,818/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 366呎 (1房)
-$847万
-$23,153/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 770呎 (3房)
-$1,452万
-$18,857/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>E | 521呎 (2房)
-$1,028万
-$19,724/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>F | 462呎 (2房)
-$968万
-$20,959/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>G | 463呎 (2房)
-$915万
-$19,765/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-$1,652万
-$21,424/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 465呎 (2房)
-$991万
-$21,308/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 366呎 (1房)
-$794万
-$21,680/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 770呎 (3房)
-$1,448万
-$18,805/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 521呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>F | 462呎 (2房)
-$964万
-$20,877/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>G | 463呎 (2房)
-$970万
-$20,942/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I23" s="18" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-$1,416万
-$18,368/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 466呎 (2房)
-$1,024万
-$21,968/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 366呎 (1房)
-$790万
-$21,596/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 770呎 (3房)
-$1,458万
-$18,931/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 521呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>F | 444呎 (2房)
-$923万
-$20,791/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>G | 459呎 (2房)
-$957万
-$20,858/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I24" s="18" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 771呎 (3房)
-$1,412万
-$18,314/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 466呎 (2房)
-$958万
-$20,569/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 366呎 (1房)
-$787万
-$21,508/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 769呎 (3房)
-$1,641万
-$21,337/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 521呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>F | 444呎 (2房)
-$864万
-$19,468/呎
-(20年-07月)</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>G | 460呎 (2房)
-$896万
-$19,487/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I25" s="18" t="inlineStr">
-        <is>
-          <t>H | 520呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 745呎 (3房)
-$1,730万
-$23,227/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 445呎 (2房)
-$963万
-$21,651/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 345呎 (1房)
-$774万
-$22,449/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 727呎 (3房)
-$1,520万
-$20,908/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,099万
-$22,030/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>F | 422呎 (2房)
-$786万
-$18,621/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>G | 438呎 (2房)
-$920万
-$20,993/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
-        <is>
-          <t>H | 498呎 (2房)
-$1,114万
-$22,369/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KOKO HILLS - 5座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>126 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>10 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>113 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$2,683万
-$34,839/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>B | 519呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 370呎 (1房)
-$1,264万
-$34,149/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 465呎 (2房)
-$1,123万
-$24,142/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>E | 459呎 (2房)
-$1,126万
-$24,529/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G6" s="21" t="inlineStr">
-        <is>
-          <t>F | 670呎 (3房)
-$2,160万
-$32,243/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,795万
-$23,317/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 519呎 (2房)
-$1,255万
-$24,189/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>C | 370呎 (1房)
-$866万
-$23,403/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>D | 465呎 (2房)
-$927万
-$19,935/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>E | 459呎 (2房)
-$960万
-$20,919/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>F | 670呎 (3房)
-$1,532万
-$22,864/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,836万
-$23,851/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,084万
-$20,850/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 370呎 (1房)
-$853万
-$23,051/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>D | 465呎 (2房)
-$952万
-$20,469/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>F | 670呎 (3房)
-$1,434万
-$21,409/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,500万
-$19,481/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 519呎 (2房)
-$1,197万
-$23,056/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 370呎 (1房)
-$894万
-$24,165/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 465呎 (2房)
-$940万
-$20,204/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>E | 459呎 (2房)
-$1,020万
-$22,227/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>F | 670呎 (3房)
-$1,458万
-$21,758/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,490万
-$19,351/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 519呎 (2房)
-$1,178万
-$22,692/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 370呎 (1房)
-$892万
-$24,105/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 465呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>F | 670呎 (3房)
-$1,423万
-$21,240/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,753万
-$22,766/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 519呎 (2房)
-$1,158万
-$22,316/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 370呎 (1房)
-$868万
-$23,462/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 465呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>E | 459呎 (2房)
-$998万
-$21,741/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>F | 670呎 (3房)
-$1,396万
-$20,843/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 519呎 (2房)
-$1,168万
-$22,511/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 370呎 (1房)
-$887万
-$23,984/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 465呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>E | 459呎 (2房)
-$988万
-$21,525/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 670呎 (3房)
-$1,435万
-$21,421/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,547万
-$20,086/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 519呎 (2房)
-$1,188万
-$22,894/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 370呎 (1房)
-$882万
-$23,827/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 465呎 (2房)
-$1,029万
-$22,129/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>E | 459呎 (2房)
-$980万
-$21,353/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 670呎 (3房)
-$1,359万
-$20,290/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,468万
-$19,065/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 519呎 (2房)
-$1,169万
-$22,524/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 370呎 (1房)
-$880万
-$23,770/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 465呎 (2房)
-$999万
-$21,492/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>E | 460呎 (2房)
-$969万
-$21,065/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>F | 671呎 (3房)
-$1,374万
-$20,483/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,644万
-$21,355/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,012万
-$19,462/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 370呎 (1房)
-$852万
-$23,019/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 465呎 (2房)
-$990万
-$21,301/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>E | 459呎 (2房)
-$1,000万
-$21,776/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>F | 670呎 (3房)
-$1,369万
-$20,433/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,503万
-$19,516/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,009万
-$19,404/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 370呎 (1房)
-$850万
-$22,962/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 465呎 (2房)
-$999万
-$21,486/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>E | 460呎 (2房)
-$998万
-$21,702/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>F | 670呎 (3房)
-$1,381万
-$20,610/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,528万
-$19,847/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,006万
-$19,346/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 370呎 (1房)
-$826万
-$22,338/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 465呎 (2房)
-$995万
-$21,402/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>E | 459呎 (2房)
-$998万
-$21,739/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>F | 670呎 (3房)
-$1,375万
-$20,527/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,494万
-$19,399/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 519呎 (2房)
-$1,122万
-$21,617/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 370呎 (1房)
-$849万
-$22,957/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 465呎 (2房)
-$1,010万
-$21,718/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>E | 460呎 (2房)
-$994万
-$21,604/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>F | 670呎 (3房)
-$1,333万
-$19,890/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,446万
-$18,779/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,010万
-$19,423/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 370呎 (1房)
-$825万
-$22,300/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 465呎 (2房)
-$993万
-$21,363/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>E | 459呎 (2房)
-$992万
-$21,610/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>F | 671呎 (3房)
-$1,382万
-$20,590/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,485万
-$19,283/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 519呎 (2房)
-$1,113万
-$21,443/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 370呎 (1房)
-$796万
-$21,508/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 465呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 459呎 (2房)
-$990万
-$21,566/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 671呎 (3房)
-$1,376万
-$20,507/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,001万
-$19,248/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 370呎 (1房)
-$815万
-$22,035/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 465呎 (2房)
-$994万
-$21,374/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>E | 459呎 (2房)
-$984万
-$21,438/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 671呎 (3房)
-$1,230万
-$18,331/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,472万
-$19,110/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$998万
-$19,190/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 370呎 (1房)
-$833万
-$22,503/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 465呎 (2房)
-$959万
-$20,632/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>E | 459呎 (2房)
-$982万
-$21,394/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>F | 671呎 (3房)
-$1,226万
-$18,271/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,410万
-$18,312/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$985万
-$18,940/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 370呎 (1房)
-$829万
-$22,414/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 465呎 (2房)
-$986万
-$21,204/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>E | 459呎 (2房)
-$980万
-$21,353/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>F | 671呎 (3房)
-$1,247万
-$18,583/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,570万
-$20,396/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,016万
-$19,546/呎
-(21年-10月)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 370呎 (1房)
-$841万
-$22,738/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 465呎 (2房)
-$982万
-$21,120/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>E | 459呎 (2房)
-$978万
-$21,309/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>F | 671呎 (3房)
-$1,243万
-$18,525/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 770呎 (3房)
-$1,387万
-$18,012/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 519呎 (2房)
-$1,045万
-$20,127/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 370呎 (1房)
-$858万
-$23,195/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 465呎 (2房)
-$978万
-$21,034/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>E | 459呎 (2房)
-$976万
-$21,266/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>F | 671呎 (3房)
-$1,252万
-$18,654/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 727呎 (3房)
-$1,634万
-$22,481/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$942万
-$18,119/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 370呎 (1房)
-$1,012万
-$27,341/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 465呎 (2房)
-$974万
-$20,951/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>E | 459呎 (2房)
-$974万
-$21,224/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>F | 647呎 (3房)
-$1,359万
-$20,998/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-茶果岭、油塘及鲤鱼门-KOKO HILLS.xlsx
+++ b/files/九龙-茶果岭、油塘及鲤鱼门-KOKO HILLS.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +44,107 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +155,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +236,66 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +672,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -19739,4 +19937,4228 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 725呎 (3房)
+$1805万
+$24,894/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>E | 736呎 (3房)
+$1754万
+$23,832/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>F | 522呎 (2房)
+$1269万
+$24,310/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>G | 570呎 (3房)
+$1471万
+$25,800/呎
+(21年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>23&amp;25</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2024呎 (4+房)
+$6274万
+$31,000/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1780呎 (4+房)
+$4800万
+$26,966/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 671呎 (3房)
+$1332万
+$19,851/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>E | 736呎 (3房)
+$1470万
+$19,973/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 522呎 (2房)
+$1074万
+$20,579/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>G | 570呎 (3房)
+$1177万
+$20,642/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 1300呎 (4+房)
+$2659万
+$20,457/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2140万
+$23,802/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 671呎 (3房)
+$1339万
+$19,954/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1732万
+$23,494/呎
+(22年-03月)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 522呎 (2房)
+$1152万
+$22,073/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 570呎 (3房)
+$1156万
+$20,272/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 1300呎 (4+房)
+$3033万
+$23,331/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2116万
+$23,533/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 671呎 (3房)
+$1330万
+$19,821/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 736呎 (3房)
+$1460万
+$19,840/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 522呎 (2房)
+$1156万
+$22,151/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 570呎 (3房)
+$1247万
+$21,884/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 1300呎 (4+房)
+$2538万
+$19,523/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2097万
+$23,324/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 671呎 (3房)
+$1358万
+$20,231/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1639万
+$22,233/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 522呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 584呎 (3房)
+$1248万
+$21,368/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 1300呎 (4+房)
+$2783万
+$21,408/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2114万
+$23,513/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr"/>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 671呎 (3房)
+$1354万
+$20,171/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1674万
+$22,708/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 522呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 584呎 (3房)
+$1253万
+$21,450/呎
+(22年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 1300呎 (4+房)
+$2550万
+$19,615/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2146万
+$23,873/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 671呎 (3房)
+$1310万
+$19,523/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 736呎 (2房)
+$1681万
+$22,840/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 522呎 (2房)
+$1058万
+$20,261/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 584呎 (3房)
+$1130万
+$19,342/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 1300呎 (4+房)
+$2554万
+$19,646/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2116万
+$23,539/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 671呎 (3房)
+$1341万
+$19,991/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1613万
+$21,882/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 522呎 (2房)
+$1031万
+$19,745/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 584呎 (3房)
+$1253万
+$21,461/呎
+(23年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 1300呎 (4+房)
+$2550万
+$19,615/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2082万
+$23,155/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 671呎 (3房)
+$1300万
+$19,374/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 736呎 (3房)
+$1647万
+$22,379/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 522呎 (2房)
+$1074万
+$20,573/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 584呎 (3房)
+$1282万
+$21,952/呎
+(20年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 1300呎 (4+房)
+$2565万
+$19,731/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2048万
+$22,781/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 671呎 (3房)
+$1333万
+$19,870/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1592万
+$21,598/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 522呎 (2房)
+$1097万
+$21,013/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>G | 584呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 1300呎 (4+房)
+$2558万
+$19,678/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2089万
+$23,236/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 671呎 (3房)
+$1330万
+$19,821/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 736呎 (3房)
+$1431万
+$19,440/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 522呎 (2房)
+$1065万
+$20,410/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 584呎 (3房)
+$1196万
+$20,474/呎
+(20年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 1300呎 (4+房)
+$2576万
+$19,814/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$1765万
+$19,633/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr"/>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 671呎 (3房)
+$1325万
+$19,753/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 736呎 (3房)
+$1391万
+$18,899/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 522呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>G | 584呎 (3房)
+$1267万
+$21,690/呎
+(20年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 1300呎 (4+房)
+$2568万
+$19,755/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$1708万
+$18,999/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr"/>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 671呎 (3房)
+$1321万
+$19,693/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 736呎 (3房)
+$1410万
+$19,158/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 522呎 (2房)
+$1057万
+$20,247/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 584呎 (3房)
+$1213万
+$20,777/呎
+(21年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 1300呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$1702万
+$18,932/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr"/>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 671呎 (3房)
+$1318万
+$19,635/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 736呎 (3房)
+$1420万
+$19,287/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 522呎 (2房)
+$1053万
+$20,167/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>G | 584呎 (3房)
+$1224万
+$20,954/呎
+(23年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 1300呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$1720万
+$19,132/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr"/>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 671呎 (3房)
+$1300万
+$19,382/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 736呎 (3房)
+$1415万
+$19,230/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 522呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 584呎 (3房)
+$1093万
+$18,712/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 1300呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$1707万
+$18,988/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr"/>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 671呎 (3房)
+$1293万
+$19,265/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1595万
+$21,647/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 522呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 584呎 (3房)
+$1104万
+$18,901/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 1300呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$1719万
+$19,120/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr"/>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 671呎 (3房)
+$1289万
+$19,209/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1542万
+$20,920/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 522呎 (2房)
+$1062万
+$20,354/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>G | 584呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 1300呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$1714万
+$19,063/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr"/>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 671呎 (3房)
+$1324万
+$19,729/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1416万
+$19,220/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 522呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>G | 584呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>A | 1300呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr"/>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 671呎 (3房)
+$1294万
+$19,285/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 736呎 (3房)
+$1390万
+$18,886/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 522呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 570呎 (3房)
+$1078万
+$18,921/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr"/>
+      <c r="C25" s="20" t="inlineStr"/>
+      <c r="D25" s="20" t="inlineStr"/>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 652呎 (3房)
+$1307万
+$20,046/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 736呎 (3房)
+$1451万
+$19,709/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 522呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 546呎 (3房)
+$1074万
+$19,674/呎
+(20年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>1&amp;2</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 1850呎 (4+房)
+$4250万
+$22,975/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 1518呎 (4+房)
+$2940万
+$19,368/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 1212呎 (4+房)
+$2968万
+$24,488/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr"/>
+      <c r="F26" s="20" t="inlineStr"/>
+      <c r="G26" s="20" t="inlineStr"/>
+      <c r="H26" s="20" t="inlineStr"/>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr"/>
+      <c r="C27" s="20" t="inlineStr"/>
+      <c r="D27" s="20" t="inlineStr"/>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 634呎 (3房)
+$1528万
+$24,106/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1519万
+$21,856/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 501呎 (2房)
+$1052万
+$20,994/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 524呎 (3房)
+$1134万
+$21,641/呎
+(20年-08月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>A | 1223呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 1102呎 (3房)
+$2880万
+$26,134/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>E | 1073呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>G | 1068呎 (3房)
+$2583万
+$24,185/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1796万
+$23,329/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$1069万
+$22,938/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 366呎 (1房)
+$867万
+$23,680/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 769呎 (3房)
+$1671万
+$21,727/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 521呎 (2房)
+$1205万
+$23,129/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 444呎 (2房)
+$964万
+$21,723/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 459呎 (2房)
+$1000万
+$21,791/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$1134万
+$21,813/呎
+(21年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+$1741万
+$22,576/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$1049万
+$22,511/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 366呎 (1房)
+$1067万
+$29,161/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 769呎 (3房)
+$1664万
+$21,640/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>E | 521呎 (2房)
+$1128万
+$21,658/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 444呎 (2房)
+$997万
+$22,464/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>G | 459呎 (2房)
+$996万
+$21,704/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$1158万
+$22,279/呎
+(22年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1786万
+$23,200/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$1099万
+$23,575/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 366呎 (1房)
+$878万
+$23,997/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 769呎 (3房)
+$1657万
+$21,553/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>E | 521呎 (2房)
+$1118万
+$21,466/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 444呎 (2房)
+$982万
+$22,126/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 459呎 (2房)
+$1019万
+$22,196/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$1120万
+$21,533/呎
+(21年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1668万
+$21,664/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 465呎 (2房)
+$1026万
+$22,060/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 366呎 (1房)
+$1062万
+$29,014/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 770呎 (3房)
+$1500万
+$19,481/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 521呎 (2房)
+$1103万
+$21,169/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 462呎 (2房)
+$964万
+$20,877/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 463呎 (2房)
+$1000万
+$21,598/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1662万
+$21,578/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 366呎 (1房)
+$832万
+$22,721/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 770呎 (3房)
+$1496万
+$19,429/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 521呎 (2房)
+$1082万
+$20,774/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 462呎 (2房)
+$959万
+$20,753/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 463呎 (2房)
+$995万
+$21,482/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$1084万
+$20,840/呎
+(21年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1760万
+$22,860/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 366呎 (1房)
+$830万
+$22,667/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 769呎 (3房)
+$1675万
+$21,784/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 521呎 (2房)
+$1078万
+$20,691/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 462呎 (2房)
+$955万
+$20,669/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 463呎 (2房)
+$1021万
+$22,056/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$1134万
+$21,813/呎
+(20年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1642万
+$21,321/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$1010万
+$21,665/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 366呎 (1房)
+$824万
+$22,516/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 769呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 521呎 (2房)
+$1097万
+$21,050/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 462呎 (2房)
+$947万
+$20,506/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 463呎 (2房)
+$952万
+$20,570/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$1071万
+$20,592/呎
+(20年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+$1656万
+$21,479/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$1006万
+$21,579/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 366呎 (1房)
+$864万
+$23,607/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 770呎 (3房)
+$1506万
+$19,565/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 521呎 (2房)
+$1065万
+$20,445/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 462呎 (2房)
+$944万
+$20,424/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 463呎 (2房)
+$949万
+$20,488/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$1066万
+$20,510/呎
+(20年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1681万
+$21,826/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$1017万
+$21,815/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 366呎 (1房)
+$872万
+$23,833/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 770呎 (3房)
+$1502万
+$19,506/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 521呎 (2房)
+$1029万
+$19,754/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 462呎 (2房)
+$1000万
+$21,639/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 463呎 (2房)
+$945万
+$20,406/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$1062万
+$20,427/呎
+(20年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1622万
+$21,068/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$998万
+$21,406/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 366呎 (1房)
+$860万
+$23,489/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 769呎 (3房)
+$1708万
+$22,205/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 521呎 (2房)
+$1057万
+$20,282/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 462呎 (2房)
+$996万
+$21,552/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 463呎 (2房)
+$965万
+$20,842/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$1092万
+$20,994/呎
+(21年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1616万
+$20,983/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$994万
+$21,322/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 366呎 (1房)
+$816万
+$22,295/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 770呎 (3房)
+$1529万
+$19,853/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 521呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 462呎 (2房)
+$932万
+$20,182/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 463呎 (2房)
+$997万
+$21,533/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$1054万
+$20,265/呎
+(20年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1650万
+$21,432/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 465呎 (2房)
+$990万
+$21,282/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 366呎 (1房)
+$864万
+$23,620/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 769呎 (3房)
+$1593万
+$20,710/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 521呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 462呎 (2房)
+$988万
+$21,381/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>G | 463呎 (2房)
+$963万
+$20,806/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+$1050万
+$20,185/呎
+(20年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1654万
+$21,479/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 465呎 (2房)
+$986万
+$21,198/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 366呎 (1房)
+$810万
+$22,117/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 769呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 521呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 462呎 (2房)
+$984万
+$21,294/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 463呎 (2房)
+$960万
+$20,724/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1596万
+$20,734/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$982万
+$21,069/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 366呎 (1房)
+$837万
+$22,872/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 769呎 (3房)
+$1580万
+$20,545/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 521呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 462呎 (2房)
+$980万
+$21,210/呎
+(20年-09月)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>G | 463呎 (2房)
+$956万
+$20,641/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+$1584万
+$20,542/呎
+(20年-09月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 465呎 (2房)
+$974万
+$20,946/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 366呎 (1房)
+$825万
+$22,552/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 770呎 (3房)
+$1486万
+$19,292/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 521呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 462呎 (2房)
+$949万
+$20,539/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 463呎 (2房)
+$977万
+$21,108/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+$1578万
+$20,460/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$970万
+$20,818/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 366呎 (1房)
+$847万
+$23,153/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 770呎 (3房)
+$1452万
+$18,857/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 521呎 (2房)
+$1028万
+$19,724/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 462呎 (2房)
+$968万
+$20,959/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 463呎 (2房)
+$915万
+$19,765/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+$1652万
+$21,424/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 465呎 (2房)
+$991万
+$21,308/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 366呎 (1房)
+$794万
+$21,680/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 770呎 (3房)
+$1448万
+$18,805/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 521呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 462呎 (2房)
+$964万
+$20,877/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>G | 463呎 (2房)
+$970万
+$20,942/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+$1416万
+$18,368/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$1024万
+$21,968/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 366呎 (1房)
+$790万
+$21,596/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 770呎 (3房)
+$1458万
+$18,931/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 521呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 444呎 (2房)
+$923万
+$20,791/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>G | 459呎 (2房)
+$957万
+$20,858/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 771呎 (3房)
+$1412万
+$18,314/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 466呎 (2房)
+$958万
+$20,569/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 366呎 (1房)
+$787万
+$21,508/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 769呎 (3房)
+$1641万
+$21,337/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 521呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 444呎 (2房)
+$864万
+$19,468/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 460呎 (2房)
+$896万
+$19,487/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>H | 520呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 745呎 (3房)
+$1730万
+$23,227/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 445呎 (2房)
+$963万
+$21,651/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 345呎 (1房)
+$774万
+$22,449/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 727呎 (3房)
+$1520万
+$20,908/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1099万
+$22,030/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 422呎 (2房)
+$786万
+$18,621/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 438呎 (2房)
+$920万
+$20,993/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>H | 498呎 (2房)
+$1114万
+$22,369/呎
+(22年-02月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$2683万
+$34,839/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>B | 519呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 370呎 (1房)
+$1264万
+$34,149/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 465呎 (2房)
+$1123万
+$24,142/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>E | 459呎 (2房)
+$1126万
+$24,529/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="G5" s="25" t="inlineStr">
+        <is>
+          <t>F | 670呎 (3房)
+$2160万
+$32,243/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1795万
+$23,317/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 519呎 (2房)
+$1255万
+$24,189/呎
+(22年-11月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 370呎 (1房)
+$866万
+$23,403/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 465呎 (2房)
+$927万
+$19,935/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 459呎 (2房)
+$960万
+$20,919/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 670呎 (3房)
+$1532万
+$22,864/呎
+(20年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1836万
+$23,851/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1084万
+$20,850/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 370呎 (1房)
+$853万
+$23,051/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 465呎 (2房)
+$952万
+$20,469/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 670呎 (3房)
+$1434万
+$21,409/呎
+(21年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1500万
+$19,481/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 519呎 (2房)
+$1197万
+$23,056/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 370呎 (1房)
+$894万
+$24,165/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 465呎 (2房)
+$940万
+$20,204/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>E | 459呎 (2房)
+$1020万
+$22,227/呎
+(22年-04月)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 670呎 (3房)
+$1458万
+$21,758/呎
+(20年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1490万
+$19,351/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 519呎 (2房)
+$1178万
+$22,692/呎
+(22年-04月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 370呎 (1房)
+$892万
+$24,105/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 465呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 670呎 (3房)
+$1423万
+$21,240/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1753万
+$22,766/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 519呎 (2房)
+$1158万
+$22,316/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 370呎 (1房)
+$868万
+$23,462/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 465呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 459呎 (2房)
+$998万
+$21,741/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 670呎 (3房)
+$1396万
+$20,843/呎
+(21年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 519呎 (2房)
+$1168万
+$22,511/呎
+(22年-04月)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 370呎 (1房)
+$887万
+$23,984/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 465呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 459呎 (2房)
+$988万
+$21,525/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 670呎 (3房)
+$1435万
+$21,421/呎
+(21年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1547万
+$20,086/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 519呎 (2房)
+$1188万
+$22,894/呎
+(22年-11月)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 370呎 (1房)
+$882万
+$23,827/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 465呎 (2房)
+$1029万
+$22,129/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 459呎 (2房)
+$980万
+$21,353/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 670呎 (3房)
+$1359万
+$20,290/呎
+(21年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1468万
+$19,065/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 519呎 (2房)
+$1169万
+$22,524/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 370呎 (1房)
+$880万
+$23,770/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 465呎 (2房)
+$999万
+$21,492/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 460呎 (2房)
+$969万
+$21,065/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 671呎 (3房)
+$1374万
+$20,483/呎
+(21年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1644万
+$21,355/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1012万
+$19,462/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 370呎 (1房)
+$852万
+$23,019/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 465呎 (2房)
+$990万
+$21,301/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 459呎 (2房)
+$1000万
+$21,776/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 670呎 (3房)
+$1369万
+$20,433/呎
+(21年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1503万
+$19,516/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1009万
+$19,404/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 370呎 (1房)
+$850万
+$22,962/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 465呎 (2房)
+$999万
+$21,486/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 460呎 (2房)
+$998万
+$21,702/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 670呎 (3房)
+$1381万
+$20,610/呎
+(22年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1528万
+$19,847/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1006万
+$19,346/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 370呎 (1房)
+$826万
+$22,338/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 465呎 (2房)
+$995万
+$21,402/呎
+(22年-03月)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 459呎 (2房)
+$998万
+$21,739/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 670呎 (3房)
+$1375万
+$20,527/呎
+(22年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1494万
+$19,399/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 519呎 (2房)
+$1122万
+$21,617/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 370呎 (1房)
+$849万
+$22,957/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 465呎 (2房)
+$1010万
+$21,718/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 460呎 (2房)
+$994万
+$21,604/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 670呎 (3房)
+$1333万
+$19,890/呎
+(20年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1446万
+$18,779/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1010万
+$19,423/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 370呎 (1房)
+$825万
+$22,300/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 465呎 (2房)
+$993万
+$21,363/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 459呎 (2房)
+$992万
+$21,610/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 671呎 (3房)
+$1382万
+$20,590/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1485万
+$19,283/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 519呎 (2房)
+$1113万
+$21,443/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 370呎 (1房)
+$796万
+$21,508/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 465呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 459呎 (2房)
+$990万
+$21,566/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 671呎 (3房)
+$1376万
+$20,507/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1001万
+$19,248/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 370呎 (1房)
+$815万
+$22,035/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 465呎 (2房)
+$994万
+$21,374/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 459呎 (2房)
+$984万
+$21,438/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 671呎 (3房)
+$1230万
+$18,331/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1472万
+$19,110/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$998万
+$19,190/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 370呎 (1房)
+$833万
+$22,503/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 465呎 (2房)
+$959万
+$20,632/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 459呎 (2房)
+$982万
+$21,394/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 671呎 (3房)
+$1226万
+$18,271/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1410万
+$18,312/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$985万
+$18,940/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 370呎 (1房)
+$829万
+$22,414/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 465呎 (2房)
+$986万
+$21,204/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 459呎 (2房)
+$980万
+$21,353/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 671呎 (3房)
+$1247万
+$18,583/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1570万
+$20,396/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1016万
+$19,546/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 370呎 (1房)
+$841万
+$22,738/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 465呎 (2房)
+$982万
+$21,120/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 459呎 (2房)
+$978万
+$21,309/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 671呎 (3房)
+$1243万
+$18,525/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 770呎 (3房)
+$1387万
+$18,012/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 519呎 (2房)
+$1045万
+$20,127/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 370呎 (1房)
+$858万
+$23,195/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 465呎 (2房)
+$978万
+$21,034/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 459呎 (2房)
+$976万
+$21,266/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 671呎 (3房)
+$1252万
+$18,654/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 727呎 (3房)
+$1634万
+$22,481/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$942万
+$18,119/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 370呎 (1房)
+$1012万
+$27,341/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 465呎 (2房)
+$974万
+$20,951/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 459呎 (2房)
+$974万
+$21,224/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 647呎 (3房)
+$1359万
+$20,998/呎
+(21年-01月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-茶果岭、油塘及鲤鱼门-KOKO HILLS.xlsx
+++ b/files/九龙-茶果岭、油塘及鲤鱼门-KOKO HILLS.xlsx
@@ -672,7 +672,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -21180,10 +21180,52 @@
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr"/>
+      <c r="C26" s="20" t="inlineStr"/>
+      <c r="D26" s="20" t="inlineStr"/>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 634呎 (3房)
+$1528万
+$24,106/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1519万
+$21,856/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>F | 501呎 (2房)
+$1052万
+$20,994/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>G | 524呎 (3房)
+$1134万
+$21,641/呎
+(20年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
           <t>1&amp;2</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>A | 1850呎 (4+房)
 $4250万
@@ -21191,7 +21233,7 @@
 (20年-07月)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>B | 1518呎 (4+房)
 $2940万
@@ -21199,7 +21241,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 1212呎 (4+房)
 $2968万
@@ -21207,52 +21249,10 @@
 (20年-08月)</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr"/>
-      <c r="F26" s="20" t="inlineStr"/>
-      <c r="G26" s="20" t="inlineStr"/>
-      <c r="H26" s="20" t="inlineStr"/>
-    </row>
-    <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="inlineStr"/>
-      <c r="C27" s="20" t="inlineStr"/>
-      <c r="D27" s="20" t="inlineStr"/>
-      <c r="E27" s="21" t="inlineStr">
-        <is>
-          <t>D | 634呎 (3房)
-$1528万
-$24,106/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F27" s="21" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1519万
-$21,856/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G27" s="21" t="inlineStr">
-        <is>
-          <t>F | 501呎 (2房)
-$1052万
-$20,994/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H27" s="21" t="inlineStr">
-        <is>
-          <t>G | 524呎 (3房)
-$1134万
-$21,641/呎
-(20年-08月)</t>
-        </is>
-      </c>
+      <c r="E27" s="20" t="inlineStr"/>
+      <c r="F27" s="20" t="inlineStr"/>
+      <c r="G27" s="20" t="inlineStr"/>
+      <c r="H27" s="20" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/files/九龙-茶果岭、油塘及鲤鱼门-KOKO HILLS.xlsx
+++ b/files/九龙-茶果岭、油塘及鲤鱼门-KOKO HILLS.xlsx
@@ -9642,14 +9642,14 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="K143" s="5" t="n">
-        <v>8591765</v>
+        <v>9018685</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>23475</v>
+        <v>24641</v>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
@@ -10642,14 +10642,14 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="K159" s="5" t="n">
-        <v>8548295</v>
+        <v>8973055</v>
       </c>
       <c r="L159" s="5" t="n">
-        <v>23356</v>
+        <v>24517</v>
       </c>
       <c r="M159" s="3" t="inlineStr">
         <is>
@@ -18916,14 +18916,14 @@
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="K290" s="5" t="n">
-        <v>17390415</v>
+        <v>18254535</v>
       </c>
       <c r="L290" s="5" t="n">
-        <v>25956</v>
+        <v>27246</v>
       </c>
       <c r="M290" s="3" t="inlineStr">
         <is>
@@ -19102,14 +19102,14 @@
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="K293" s="5" t="n">
-        <v>10171175</v>
+        <v>10676575</v>
       </c>
       <c r="L293" s="5" t="n">
-        <v>27490</v>
+        <v>28856</v>
       </c>
       <c r="M293" s="3" t="inlineStr">
         <is>
@@ -26614,14 +26614,14 @@
       </c>
       <c r="J413" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="K413" s="5" t="n">
-        <v>8143380</v>
+        <v>8548020</v>
       </c>
       <c r="L413" s="5" t="n">
-        <v>22009</v>
+        <v>23103</v>
       </c>
       <c r="M413" s="3" t="inlineStr">
         <is>
